--- a/data/gravel/Rose Backroad FF 2025.xlsx
+++ b/data/gravel/Rose Backroad FF 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15389095-D866-254C-B547-9EDB0615B44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB23A27-3EE5-9D48-94C0-715E781C5BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6440" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3080" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Rose Backroad FF 2025.xlsx
+++ b/data/gravel/Rose Backroad FF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB23A27-3EE5-9D48-94C0-715E781C5BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DFFDFD-5BF5-5848-87D3-EE2B5ED2A780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="196">
   <si>
     <t>brand</t>
   </si>
@@ -868,6 +868,9 @@
   </si>
   <si>
     <t>stack_plus_reach_plus</t>
+  </si>
+  <si>
+    <t>https://cdn.rosebikes.de/cms/cms.65e72b4b48ede7.00076604.png?im=Resize=(2880)</t>
   </si>
 </sst>
 </file>
@@ -1271,6 +1274,11 @@
         <v>76</v>
       </c>
     </row>
+    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>

--- a/data/gravel/Rose Backroad FF 2025.xlsx
+++ b/data/gravel/Rose Backroad FF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DFFDFD-5BF5-5848-87D3-EE2B5ED2A780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F3C3F8-3B66-4248-AEBC-93BD08EDAC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9800" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="198">
   <si>
     <t>brand</t>
   </si>
@@ -852,9 +852,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>euro</t>
-  </si>
-  <si>
     <t>integrated</t>
   </si>
   <si>
@@ -871,6 +868,15 @@
   </si>
   <si>
     <t>https://cdn.rosebikes.de/cms/cms.65e72b4b48ede7.00076604.png?im=Resize=(2880)</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bocholt, Germany</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI78"/>
+  <dimension ref="A1:BI79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1276,7 +1282,7 @@
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.3">
@@ -2595,7 +2601,7 @@
     </row>
     <row r="17" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>135</v>
@@ -2726,7 +2732,7 @@
     </row>
     <row r="19" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>136</v>
@@ -2782,7 +2788,7 @@
     </row>
     <row r="21" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>137</v>
@@ -2866,7 +2872,7 @@
     </row>
     <row r="24" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>142</v>
@@ -3458,7 +3464,7 @@
         <v>55</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -3540,7 +3546,15 @@
         <v>69</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Rose Backroad FF 2025.xlsx
+++ b/data/gravel/Rose Backroad FF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F3C3F8-3B66-4248-AEBC-93BD08EDAC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E340E2-0BA5-194D-A73A-46D1C7E2A43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9800" yWindow="500" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28480" yWindow="-18400" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="196">
   <si>
     <t>brand</t>
   </si>
@@ -840,15 +840,6 @@
     <t>system_weight</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
-    <t>a8:h38</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -877,6 +868,9 @@
   </si>
   <si>
     <t>Bocholt, Germany</t>
+  </si>
+  <si>
+    <t>a8:h36</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI79"/>
+  <dimension ref="A1:BI77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1282,7 +1276,7 @@
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.3">
@@ -1290,7 +1284,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -2601,7 +2595,7 @@
     </row>
     <row r="17" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>135</v>
@@ -2732,7 +2726,7 @@
     </row>
     <row r="19" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>136</v>
@@ -2788,7 +2782,7 @@
     </row>
     <row r="21" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>137</v>
@@ -2872,7 +2866,7 @@
     </row>
     <row r="24" spans="1:35" ht="22" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>142</v>
@@ -3169,29 +3163,29 @@
       <c r="B35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="3">
-        <f>C37</f>
+      <c r="C35" s="1">
+        <f>VALUE(LEFT(C$37,3))</f>
         <v>157</v>
       </c>
-      <c r="D35" s="3">
-        <f>AVERAGE(D37,C38)</f>
+      <c r="D35" s="1">
+        <f>VALUE(LEFT(D$37,3))</f>
         <v>168</v>
       </c>
-      <c r="E35" s="3">
-        <f t="shared" ref="E35:H35" si="0">AVERAGE(E37,D38)</f>
-        <v>175</v>
-      </c>
-      <c r="F35" s="3">
-        <f t="shared" si="0"/>
-        <v>180</v>
-      </c>
-      <c r="G35" s="3">
-        <f t="shared" si="0"/>
-        <v>184.5</v>
-      </c>
-      <c r="H35" s="3">
-        <f t="shared" si="0"/>
-        <v>192</v>
+      <c r="E35" s="1">
+        <f>VALUE(LEFT(E$37,3))</f>
+        <v>174</v>
+      </c>
+      <c r="F35" s="1">
+        <f>VALUE(LEFT(F$37,3))</f>
+        <v>179</v>
+      </c>
+      <c r="G35" s="1">
+        <f>VALUE(LEFT(G$37,3))</f>
+        <v>183</v>
+      </c>
+      <c r="H35" s="1">
+        <f>VALUE(LEFT(H$37,3))</f>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -3201,360 +3195,300 @@
       <c r="B36" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="3">
-        <f>D35</f>
+      <c r="C36" s="1">
+        <f>VALUE(RIGHT(C$37,3))</f>
         <v>168</v>
       </c>
-      <c r="D36" s="3">
-        <f t="shared" ref="D36:G36" si="1">E35</f>
-        <v>175</v>
-      </c>
-      <c r="E36" s="3">
-        <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="F36" s="3">
-        <f t="shared" si="1"/>
-        <v>184.5</v>
-      </c>
-      <c r="G36" s="3">
-        <f t="shared" si="1"/>
-        <v>192</v>
-      </c>
-      <c r="H36" s="3">
-        <f>H38</f>
+      <c r="D36" s="1">
+        <f>VALUE(RIGHT(D$37,3))</f>
+        <v>176</v>
+      </c>
+      <c r="E36" s="1">
+        <f>VALUE(RIGHT(E$37,3))</f>
+        <v>181</v>
+      </c>
+      <c r="F36" s="1">
+        <f>VALUE(RIGHT(F$37,3))</f>
+        <v>186</v>
+      </c>
+      <c r="G36" s="1">
+        <f>VALUE(RIGHT(G$37,3))</f>
+        <v>193</v>
+      </c>
+      <c r="H36" s="1">
+        <f>VALUE(RIGHT(H$37,3))</f>
         <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="1">
-        <f>VALUE(LEFT(C$39,3))</f>
-        <v>157</v>
-      </c>
-      <c r="D37" s="1">
-        <f t="shared" ref="D37:H37" si="2">VALUE(LEFT(D$39,3))</f>
-        <v>168</v>
-      </c>
-      <c r="E37" s="1">
-        <f t="shared" si="2"/>
-        <v>174</v>
-      </c>
-      <c r="F37" s="1">
-        <f t="shared" si="2"/>
-        <v>179</v>
-      </c>
-      <c r="G37" s="1">
-        <f t="shared" si="2"/>
-        <v>183</v>
-      </c>
-      <c r="H37" s="1">
-        <f t="shared" si="2"/>
-        <v>191</v>
+      <c r="C37" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="1">
-        <f>VALUE(RIGHT(C$39,3))</f>
-        <v>168</v>
-      </c>
-      <c r="D38" s="1">
-        <f t="shared" ref="D38:H38" si="3">VALUE(RIGHT(D$39,3))</f>
-        <v>176</v>
-      </c>
-      <c r="E38" s="1">
-        <f t="shared" si="3"/>
-        <v>181</v>
-      </c>
-      <c r="F38" s="1">
-        <f t="shared" si="3"/>
-        <v>186</v>
-      </c>
-      <c r="G38" s="1">
-        <f t="shared" si="3"/>
-        <v>193</v>
-      </c>
-      <c r="H38" s="1">
-        <f t="shared" si="3"/>
-        <v>200</v>
+      <c r="A38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C39" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>151</v>
+      <c r="A39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>188</v>
+        <v>38</v>
+      </c>
+      <c r="B45" s="1">
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="B51" s="1">
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="B52" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="1">
-        <v>142</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1">
-        <v>100</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>188</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>189</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="1">
-        <v>2</v>
+        <v>61</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>188</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="B74" s="1">
+        <v>3699</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B76" s="1">
-        <v>3699</v>
+        <v>69</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Rose Backroad FF 2025.xlsx
+++ b/data/gravel/Rose Backroad FF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E340E2-0BA5-194D-A73A-46D1C7E2A43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DEAA8D-413D-AC4C-A5D2-278EB5A34AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28480" yWindow="-18400" windowWidth="25720" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="202">
   <si>
     <t>brand</t>
   </si>
@@ -871,6 +871,24 @@
   </si>
   <si>
     <t>a8:h36</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI77"/>
+  <dimension ref="A1:BI83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -3164,27 +3182,27 @@
         <v>30</v>
       </c>
       <c r="C35" s="1">
-        <f>VALUE(LEFT(C$37,3))</f>
+        <f t="shared" ref="C35:H35" si="0">VALUE(LEFT(C$37,3))</f>
         <v>157</v>
       </c>
       <c r="D35" s="1">
-        <f>VALUE(LEFT(D$37,3))</f>
+        <f t="shared" si="0"/>
         <v>168</v>
       </c>
       <c r="E35" s="1">
-        <f>VALUE(LEFT(E$37,3))</f>
+        <f t="shared" si="0"/>
         <v>174</v>
       </c>
       <c r="F35" s="1">
-        <f>VALUE(LEFT(F$37,3))</f>
+        <f t="shared" si="0"/>
         <v>179</v>
       </c>
       <c r="G35" s="1">
-        <f>VALUE(LEFT(G$37,3))</f>
+        <f t="shared" si="0"/>
         <v>183</v>
       </c>
       <c r="H35" s="1">
-        <f>VALUE(LEFT(H$37,3))</f>
+        <f t="shared" si="0"/>
         <v>191</v>
       </c>
     </row>
@@ -3196,27 +3214,27 @@
         <v>31</v>
       </c>
       <c r="C36" s="1">
-        <f>VALUE(RIGHT(C$37,3))</f>
+        <f t="shared" ref="C36:H36" si="1">VALUE(RIGHT(C$37,3))</f>
         <v>168</v>
       </c>
       <c r="D36" s="1">
-        <f>VALUE(RIGHT(D$37,3))</f>
+        <f t="shared" si="1"/>
         <v>176</v>
       </c>
       <c r="E36" s="1">
-        <f>VALUE(RIGHT(E$37,3))</f>
+        <f t="shared" si="1"/>
         <v>181</v>
       </c>
       <c r="F36" s="1">
-        <f>VALUE(RIGHT(F$37,3))</f>
+        <f t="shared" si="1"/>
         <v>186</v>
       </c>
       <c r="G36" s="1">
-        <f>VALUE(RIGHT(G$37,3))</f>
+        <f t="shared" si="1"/>
         <v>193</v>
       </c>
       <c r="H36" s="1">
-        <f>VALUE(RIGHT(H$37,3))</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
@@ -3347,147 +3365,177 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>46</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>48</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>51</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B66" s="1">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B74" s="1">
-        <v>3699</v>
+        <v>61</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>192</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" s="1">
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>194</v>
       </c>
     </row>
